--- a/artfynd/A 24318-2023 artfynd.xlsx
+++ b/artfynd/A 24318-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24318-2023 artfynd.xlsx
+++ b/artfynd/A 24318-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112606759</v>
+        <v>113417084</v>
       </c>
       <c r="B5" t="n">
-        <v>89735</v>
+        <v>78507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,41 +1038,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Härkmyran, Lu lm</t>
+          <t>SOLÄLVEN, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782476</v>
+        <v>782406</v>
       </c>
       <c r="R5" t="n">
-        <v>7398977</v>
+        <v>7399108</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,17 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112606758</v>
+        <v>113417093</v>
       </c>
       <c r="B6" t="n">
-        <v>88855</v>
+        <v>78507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,37 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härkmyran, Lu lm</t>
+          <t>SOLÄLVEN, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782474</v>
+        <v>782683</v>
       </c>
       <c r="R6" t="n">
-        <v>7398983</v>
+        <v>7399104</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,17 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113417084</v>
+        <v>113417069</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
+        <v>57281</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782406</v>
+        <v>782503</v>
       </c>
       <c r="R7" t="n">
-        <v>7399108</v>
+        <v>7398892</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1342,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113417093</v>
+        <v>113417071</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
+        <v>57281</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782683</v>
+        <v>783052</v>
       </c>
       <c r="R8" t="n">
-        <v>7399104</v>
+        <v>7399090</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1444,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113417069</v>
+        <v>113417085</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
+        <v>78507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782503</v>
+        <v>782409</v>
       </c>
       <c r="R9" t="n">
-        <v>7398892</v>
+        <v>7398986</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1546,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113417071</v>
+        <v>113417094</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
+        <v>78507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>783052</v>
+        <v>782779</v>
       </c>
       <c r="R10" t="n">
-        <v>7399090</v>
+        <v>7398990</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1648,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113417085</v>
+        <v>113417095</v>
       </c>
       <c r="B11" t="n">
         <v>78507</v>
@@ -1688,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782409</v>
+        <v>782879</v>
       </c>
       <c r="R11" t="n">
-        <v>7398986</v>
+        <v>7399071</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1750,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113417094</v>
+        <v>113417106</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
+        <v>90897</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782779</v>
+        <v>782683</v>
       </c>
       <c r="R12" t="n">
-        <v>7398990</v>
+        <v>7399072</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1852,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113417095</v>
+        <v>113417082</v>
       </c>
       <c r="B13" t="n">
         <v>78507</v>
@@ -1892,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782879</v>
+        <v>782576</v>
       </c>
       <c r="R13" t="n">
-        <v>7399071</v>
+        <v>7399012</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1954,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113417106</v>
+        <v>113417066</v>
       </c>
       <c r="B14" t="n">
-        <v>90897</v>
+        <v>57265</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1956,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782683</v>
+        <v>782901</v>
       </c>
       <c r="R14" t="n">
-        <v>7399072</v>
+        <v>7399094</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2056,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113417082</v>
+        <v>113417099</v>
       </c>
       <c r="B15" t="n">
         <v>78507</v>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782576</v>
+        <v>783091</v>
       </c>
       <c r="R15" t="n">
-        <v>7399012</v>
+        <v>7399099</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2158,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113417066</v>
+        <v>113417081</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782901</v>
+        <v>782668</v>
       </c>
       <c r="R16" t="n">
-        <v>7399094</v>
+        <v>7399067</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2260,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113417099</v>
+        <v>113417096</v>
       </c>
       <c r="B17" t="n">
         <v>78507</v>
@@ -2300,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>783091</v>
+        <v>782947</v>
       </c>
       <c r="R17" t="n">
-        <v>7399099</v>
+        <v>7399095</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2362,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113417081</v>
+        <v>113417070</v>
       </c>
       <c r="B18" t="n">
-        <v>78507</v>
+        <v>57281</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2368,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782668</v>
+        <v>782639</v>
       </c>
       <c r="R18" t="n">
-        <v>7399067</v>
+        <v>7399072</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2464,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113417096</v>
+        <v>113417065</v>
       </c>
       <c r="B19" t="n">
-        <v>78507</v>
+        <v>57265</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782947</v>
+        <v>782514</v>
       </c>
       <c r="R19" t="n">
-        <v>7399095</v>
+        <v>7398914</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2566,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113417070</v>
+        <v>113417091</v>
       </c>
       <c r="B20" t="n">
-        <v>57281</v>
+        <v>78507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2572,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782639</v>
+        <v>782596</v>
       </c>
       <c r="R20" t="n">
-        <v>7399072</v>
+        <v>7398976</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2668,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113417065</v>
+        <v>113417101</v>
       </c>
       <c r="B21" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782514</v>
+        <v>783254</v>
       </c>
       <c r="R21" t="n">
-        <v>7398914</v>
+        <v>7399118</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2770,7 +2760,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113417091</v>
+        <v>113417089</v>
       </c>
       <c r="B22" t="n">
         <v>78507</v>
@@ -2810,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782596</v>
+        <v>782541</v>
       </c>
       <c r="R22" t="n">
-        <v>7398976</v>
+        <v>7398969</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2872,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113417101</v>
+        <v>113417092</v>
       </c>
       <c r="B23" t="n">
         <v>78507</v>
@@ -2912,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>783254</v>
+        <v>782639</v>
       </c>
       <c r="R23" t="n">
-        <v>7399118</v>
+        <v>7399098</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2974,7 +2964,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113417089</v>
+        <v>113417098</v>
       </c>
       <c r="B24" t="n">
         <v>78507</v>
@@ -3014,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>782541</v>
+        <v>783073</v>
       </c>
       <c r="R24" t="n">
-        <v>7398969</v>
+        <v>7399092</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3076,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113417092</v>
+        <v>113417078</v>
       </c>
       <c r="B25" t="n">
-        <v>78507</v>
+        <v>78589</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3092,21 +3082,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>782639</v>
+        <v>782946</v>
       </c>
       <c r="R25" t="n">
-        <v>7399098</v>
+        <v>7399095</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3178,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113417098</v>
+        <v>113417067</v>
       </c>
       <c r="B26" t="n">
-        <v>78507</v>
+        <v>57265</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,21 +3184,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3218,10 +3208,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>783073</v>
+        <v>783052</v>
       </c>
       <c r="R26" t="n">
-        <v>7399092</v>
+        <v>7399084</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3280,10 +3270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113417078</v>
+        <v>113417064</v>
       </c>
       <c r="B27" t="n">
-        <v>78589</v>
+        <v>57265</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3320,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>782946</v>
+        <v>782404</v>
       </c>
       <c r="R27" t="n">
-        <v>7399095</v>
+        <v>7398905</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3382,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113417067</v>
+        <v>113417083</v>
       </c>
       <c r="B28" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3398,21 +3388,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>783052</v>
+        <v>782426</v>
       </c>
       <c r="R28" t="n">
-        <v>7399084</v>
+        <v>7399118</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3484,10 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113417064</v>
+        <v>113417086</v>
       </c>
       <c r="B29" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3500,21 +3490,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3586,7 +3576,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113417083</v>
+        <v>113417102</v>
       </c>
       <c r="B30" t="n">
         <v>78507</v>
@@ -3626,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>782426</v>
+        <v>783258</v>
       </c>
       <c r="R30" t="n">
-        <v>7399118</v>
+        <v>7399125</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3688,7 +3678,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113417086</v>
+        <v>113417097</v>
       </c>
       <c r="B31" t="n">
         <v>78507</v>
@@ -3728,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>782404</v>
+        <v>783040</v>
       </c>
       <c r="R31" t="n">
-        <v>7398905</v>
+        <v>7399087</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3790,7 +3780,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113417102</v>
+        <v>113417087</v>
       </c>
       <c r="B32" t="n">
         <v>78507</v>
@@ -3830,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>783258</v>
+        <v>782500</v>
       </c>
       <c r="R32" t="n">
-        <v>7399125</v>
+        <v>7398896</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3892,7 +3882,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113417097</v>
+        <v>113417090</v>
       </c>
       <c r="B33" t="n">
         <v>78507</v>
@@ -3932,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>783040</v>
+        <v>782584</v>
       </c>
       <c r="R33" t="n">
-        <v>7399087</v>
+        <v>7398969</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3994,10 +3984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113417087</v>
+        <v>113417108</v>
       </c>
       <c r="B34" t="n">
-        <v>78507</v>
+        <v>79587</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4006,25 +3996,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4034,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>782500</v>
+        <v>782682</v>
       </c>
       <c r="R34" t="n">
-        <v>7398896</v>
+        <v>7399073</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4078,6 +4068,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4096,10 +4087,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113417090</v>
+        <v>113417063</v>
       </c>
       <c r="B35" t="n">
-        <v>78507</v>
+        <v>57265</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4112,21 +4103,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4136,10 +4127,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>782584</v>
+        <v>782383</v>
       </c>
       <c r="R35" t="n">
-        <v>7398969</v>
+        <v>7399015</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4198,10 +4189,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113417108</v>
+        <v>113417061</v>
       </c>
       <c r="B36" t="n">
-        <v>79587</v>
+        <v>57265</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4210,25 +4201,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4229,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>782682</v>
+        <v>782746</v>
       </c>
       <c r="R36" t="n">
-        <v>7399073</v>
+        <v>7398994</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4282,7 +4273,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4301,10 +4291,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113417063</v>
+        <v>113417088</v>
       </c>
       <c r="B37" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4317,21 +4307,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4341,10 +4331,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>782383</v>
+        <v>782532</v>
       </c>
       <c r="R37" t="n">
-        <v>7399015</v>
+        <v>7398964</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4403,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113417061</v>
+        <v>113417073</v>
       </c>
       <c r="B38" t="n">
-        <v>57265</v>
+        <v>79559</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4419,21 +4409,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4443,10 +4433,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>782746</v>
+        <v>782683</v>
       </c>
       <c r="R38" t="n">
-        <v>7398994</v>
+        <v>7399071</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4487,6 +4477,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4502,211 +4493,6 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>113417088</v>
-      </c>
-      <c r="B39" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>SOLÄLVEN, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>782532</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7398964</v>
-      </c>
-      <c r="S39" t="n">
-        <v>15</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>113417073</v>
-      </c>
-      <c r="B40" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>SOLÄLVEN, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>782683</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7399071</v>
-      </c>
-      <c r="S40" t="n">
-        <v>15</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24318-2023 artfynd.xlsx
+++ b/artfynd/A 24318-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104160204</v>
+        <v>113417106</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härkmyran, Lu lm</t>
+          <t>SOLÄLVEN, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>782473.8485789853</v>
+        <v>782683</v>
       </c>
       <c r="R2" t="n">
-        <v>7398983.178598194</v>
+        <v>7399072</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104160206</v>
+        <v>113417077</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härkmyran, Lu lm</t>
+          <t>SOLÄLVEN, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782476.04529678</v>
+        <v>782710</v>
       </c>
       <c r="R3" t="n">
-        <v>7398977.396513881</v>
+        <v>7399052</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109910038</v>
+        <v>113417078</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härkmyran, Lu lm</t>
+          <t>SOLÄLVEN, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782472.92339944</v>
+        <v>782946</v>
       </c>
       <c r="R4" t="n">
-        <v>7398988.290102297</v>
+        <v>7399095</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113417084</v>
+        <v>112606758</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SOLÄLVEN, Lu lm</t>
+          <t>Härkmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782406</v>
+        <v>782474</v>
       </c>
       <c r="R5" t="n">
-        <v>7399108</v>
+        <v>7398983</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1031,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,27 +1056,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113417093</v>
+        <v>113417073</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,7 +1106,7 @@
         <v>782683</v>
       </c>
       <c r="R6" t="n">
-        <v>7399104</v>
+        <v>7399071</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1212,6 +1147,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,53 +1166,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113417069</v>
+        <v>112606759</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SOLÄLVEN, Lu lm</t>
+          <t>Härkmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782503</v>
+        <v>782476</v>
       </c>
       <c r="R7" t="n">
-        <v>7398892</v>
+        <v>7398977</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,12 +1231,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,49 +1256,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113417071</v>
+        <v>113417081</v>
       </c>
       <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>783052</v>
+        <v>782668</v>
       </c>
       <c r="R8" t="n">
-        <v>7399090</v>
+        <v>7399067</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1434,19 +1365,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113417085</v>
+        <v>113417082</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1474,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782409</v>
+        <v>782576</v>
       </c>
       <c r="R9" t="n">
-        <v>7398986</v>
+        <v>7399012</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1536,19 +1462,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113417094</v>
+        <v>113417083</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1576,10 +1497,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782779</v>
+        <v>782426</v>
       </c>
       <c r="R10" t="n">
-        <v>7398990</v>
+        <v>7399118</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1638,19 +1559,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113417095</v>
+        <v>113417084</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1678,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782879</v>
+        <v>782406</v>
       </c>
       <c r="R11" t="n">
-        <v>7399071</v>
+        <v>7399108</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1740,15 +1656,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113417106</v>
+        <v>113417085</v>
       </c>
       <c r="B12" t="n">
-        <v>90897</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1667,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782683</v>
+        <v>782409</v>
       </c>
       <c r="R12" t="n">
-        <v>7399072</v>
+        <v>7398986</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1842,19 +1753,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113417082</v>
+        <v>113417086</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1882,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782576</v>
+        <v>782404</v>
       </c>
       <c r="R13" t="n">
-        <v>7399012</v>
+        <v>7398905</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1944,37 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113417066</v>
+        <v>113417087</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782901</v>
+        <v>782500</v>
       </c>
       <c r="R14" t="n">
-        <v>7399094</v>
+        <v>7398896</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2046,19 +1947,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113417099</v>
+        <v>113417088</v>
       </c>
       <c r="B15" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2086,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>783091</v>
+        <v>782532</v>
       </c>
       <c r="R15" t="n">
-        <v>7399099</v>
+        <v>7398964</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2148,19 +2044,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113417081</v>
+        <v>113417089</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2188,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782668</v>
+        <v>782541</v>
       </c>
       <c r="R16" t="n">
-        <v>7399067</v>
+        <v>7398969</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2250,19 +2141,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113417096</v>
+        <v>113417090</v>
       </c>
       <c r="B17" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2290,10 +2176,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782947</v>
+        <v>782584</v>
       </c>
       <c r="R17" t="n">
-        <v>7399095</v>
+        <v>7398969</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2352,37 +2238,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113417070</v>
+        <v>113417091</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2273,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782639</v>
+        <v>782596</v>
       </c>
       <c r="R18" t="n">
-        <v>7399072</v>
+        <v>7398976</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2454,37 +2335,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113417065</v>
+        <v>113417092</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782514</v>
+        <v>782639</v>
       </c>
       <c r="R19" t="n">
-        <v>7398914</v>
+        <v>7399098</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2556,19 +2432,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113417091</v>
+        <v>113417093</v>
       </c>
       <c r="B20" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2596,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782596</v>
+        <v>782683</v>
       </c>
       <c r="R20" t="n">
-        <v>7398976</v>
+        <v>7399104</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2658,19 +2529,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113417101</v>
+        <v>113417094</v>
       </c>
       <c r="B21" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2698,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>783254</v>
+        <v>782779</v>
       </c>
       <c r="R21" t="n">
-        <v>7399118</v>
+        <v>7398990</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2760,19 +2626,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113417089</v>
+        <v>113417095</v>
       </c>
       <c r="B22" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2800,10 +2661,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782541</v>
+        <v>782879</v>
       </c>
       <c r="R22" t="n">
-        <v>7398969</v>
+        <v>7399071</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2862,19 +2723,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113417092</v>
+        <v>113417096</v>
       </c>
       <c r="B23" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2902,10 +2758,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>782639</v>
+        <v>782947</v>
       </c>
       <c r="R23" t="n">
-        <v>7399098</v>
+        <v>7399095</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2964,19 +2820,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113417098</v>
+        <v>113417097</v>
       </c>
       <c r="B24" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3004,10 +2855,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>783073</v>
+        <v>783040</v>
       </c>
       <c r="R24" t="n">
-        <v>7399092</v>
+        <v>7399087</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3066,37 +2917,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113417078</v>
+        <v>113417098</v>
       </c>
       <c r="B25" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3106,10 +2952,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>782946</v>
+        <v>783073</v>
       </c>
       <c r="R25" t="n">
-        <v>7399095</v>
+        <v>7399092</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3168,37 +3014,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113417067</v>
+        <v>113417099</v>
       </c>
       <c r="B26" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3208,10 +3049,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>783052</v>
+        <v>783091</v>
       </c>
       <c r="R26" t="n">
-        <v>7399084</v>
+        <v>7399099</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3270,37 +3111,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113417064</v>
+        <v>113417101</v>
       </c>
       <c r="B27" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3146,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>782404</v>
+        <v>783254</v>
       </c>
       <c r="R27" t="n">
-        <v>7398905</v>
+        <v>7399118</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3372,19 +3208,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113417083</v>
+        <v>113417102</v>
       </c>
       <c r="B28" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3412,10 +3243,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>782426</v>
+        <v>783258</v>
       </c>
       <c r="R28" t="n">
-        <v>7399118</v>
+        <v>7399125</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3474,37 +3305,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113417086</v>
+        <v>113417107</v>
       </c>
       <c r="B29" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3514,10 +3340,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>782404</v>
+        <v>782723</v>
       </c>
       <c r="R29" t="n">
-        <v>7398905</v>
+        <v>7399050</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3558,6 +3384,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3576,37 +3403,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113417102</v>
+        <v>113417108</v>
       </c>
       <c r="B30" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3438,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>783258</v>
+        <v>782682</v>
       </c>
       <c r="R30" t="n">
-        <v>7399125</v>
+        <v>7399073</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3660,6 +3482,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3678,37 +3501,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113417097</v>
+        <v>113417069</v>
       </c>
       <c r="B31" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3536,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>783040</v>
+        <v>782503</v>
       </c>
       <c r="R31" t="n">
-        <v>7399087</v>
+        <v>7398892</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3780,37 +3598,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113417087</v>
+        <v>113417070</v>
       </c>
       <c r="B32" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3820,10 +3633,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>782500</v>
+        <v>782639</v>
       </c>
       <c r="R32" t="n">
-        <v>7398896</v>
+        <v>7399072</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3882,37 +3695,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113417090</v>
+        <v>113417071</v>
       </c>
       <c r="B33" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,10 +3730,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>782584</v>
+        <v>783052</v>
       </c>
       <c r="R33" t="n">
-        <v>7398969</v>
+        <v>7399090</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3984,37 +3792,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113417108</v>
+        <v>113417061</v>
       </c>
       <c r="B34" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4024,10 +3827,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>782682</v>
+        <v>782746</v>
       </c>
       <c r="R34" t="n">
-        <v>7399073</v>
+        <v>7398994</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4068,7 +3871,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4090,12 +3892,7 @@
         <v>113417063</v>
       </c>
       <c r="B35" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4189,15 +3986,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113417061</v>
+        <v>113417064</v>
       </c>
       <c r="B36" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,10 +4021,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>782746</v>
+        <v>782404</v>
       </c>
       <c r="R36" t="n">
-        <v>7398994</v>
+        <v>7398905</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4291,15 +4083,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113417088</v>
+        <v>113417065</v>
       </c>
       <c r="B37" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4307,21 +4094,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4331,10 +4118,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>782532</v>
+        <v>782514</v>
       </c>
       <c r="R37" t="n">
-        <v>7398964</v>
+        <v>7398914</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4393,15 +4180,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113417073</v>
+        <v>113417066</v>
       </c>
       <c r="B38" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4409,21 +4191,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,10 +4215,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>782683</v>
+        <v>782901</v>
       </c>
       <c r="R38" t="n">
-        <v>7399071</v>
+        <v>7399094</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4477,7 +4259,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4493,6 +4274,302 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>113417067</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SOLÄLVEN, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>783052</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7399084</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>113417076</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SOLÄLVEN, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>782726</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7399053</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112606770</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Härkmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>783028</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7398958</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24318-2023 artfynd.xlsx
+++ b/artfynd/A 24318-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417106</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417078</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606758</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1163,6 +1188,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417073</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1265,6 +1295,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606759</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1362,6 +1397,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417082</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1556,6 +1601,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417083</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1653,6 +1703,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417084</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417085</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1847,6 +1907,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417086</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1944,6 +2009,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417087</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2041,6 +2111,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417088</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2138,6 +2213,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417089</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2235,6 +2315,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417090</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2332,6 +2417,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417091</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2429,6 +2519,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417092</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2526,6 +2621,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417093</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2623,6 +2723,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417094</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2720,6 +2825,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417095</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2817,6 +2927,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417096</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2914,6 +3029,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417097</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3011,6 +3131,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417098</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3108,6 +3233,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417099</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3205,6 +3335,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417101</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3302,6 +3437,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417102</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3400,6 +3540,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417107</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3498,6 +3643,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417108</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3595,6 +3745,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417069</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3692,6 +3847,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417070</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3789,6 +3949,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417071</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3886,6 +4051,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417061</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3983,6 +4153,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417063</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4080,6 +4255,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417064</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4177,6 +4357,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417065</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4274,6 +4459,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417066</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4371,6 +4561,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417067</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4468,6 +4663,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113417076</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4570,8 +4770,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606770</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>